--- a/Files/KALYAN MORNING PENAL.xlsx
+++ b/Files/KALYAN MORNING PENAL.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$193</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$195</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -1586,6 +1586,12 @@
   </x:si>
   <x:si>
     <x:t>31/08/2026 to 06/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026 to 13/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026 to 20/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -2044,7 +2050,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V193"/>
+  <x:dimension ref="A1:V195"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -15121,62 +15127,198 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="E193" s="3" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F193" s="3" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G193" s="3" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H193" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I193" s="3" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="J193" s="3" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K193" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L193" s="3" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="M193" s="3" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="N193" s="3" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="O193" s="3" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="P193" s="3" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="Q193" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="R193" s="3" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="S193" s="3" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="T193" s="3" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="U193" s="3" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="V193" s="3" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:22">
+      <x:c r="A194" s="3" t="s">
         <x:v>523</x:v>
       </x:c>
-      <x:c r="F193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="G193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="H193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="I193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="J193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="K193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="L193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="M193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="N193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="O193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="P193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="Q193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="R193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="S193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="T193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="U193" s="3" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="V193" s="3" t="s">
-        <x:v>523</x:v>
+      <x:c r="B194" s="3" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C194" s="3" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D194" s="3" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="E194" s="3" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F194" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G194" s="3" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H194" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I194" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J194" s="3" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="K194" s="3" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="L194" s="3" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="M194" s="3" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="N194" s="3" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="O194" s="3" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="P194" s="3" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="Q194" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="R194" s="3" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="S194" s="3" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="T194" s="3" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="U194" s="3" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="V194" s="3" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:22">
+      <x:c r="A195" s="3" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B195" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C195" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D195" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="F195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="G195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="H195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="I195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="J195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="K195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="L195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="M195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="N195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="O195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="P195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="Q195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="R195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="S195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="T195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="U195" s="3" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="V195" s="3" t="s">
+        <x:v>525</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V193"/>
+  <x:autoFilter ref="A1:V195"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -15199,39 +15341,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>524</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>525</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>526</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>527</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>528</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>529</x:v>
+        <x:v>531</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>530</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -15239,10 +15381,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>532</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>522</x:v>
+        <x:v>524</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/KALYAN MORNING PENAL.xlsx
+++ b/Files/KALYAN MORNING PENAL.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$195</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$196</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -1592,6 +1592,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 20/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 27/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -2050,7 +2053,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V195"/>
+  <x:dimension ref="A1:V196"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -15263,62 +15266,130 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E195" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F195" s="3" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G195" s="3" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H195" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I195" s="3" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="J195" s="3" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="K195" s="3" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="L195" s="3" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="M195" s="3" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="N195" s="3" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="O195" s="3" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="P195" s="3" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="Q195" s="3" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="R195" s="3" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="S195" s="3" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="T195" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="U195" s="3" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="V195" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:22">
+      <x:c r="A196" s="3" t="s">
         <x:v>525</x:v>
       </x:c>
-      <x:c r="F195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="G195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="H195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="I195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="J195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="K195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="L195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="M195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="N195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="O195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="P195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="Q195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="R195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="S195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="T195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="U195" s="3" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="V195" s="3" t="s">
-        <x:v>525</x:v>
+      <x:c r="B196" s="3" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C196" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D196" s="3" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="E196" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F196" s="3" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G196" s="3" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H196" s="3" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I196" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J196" s="3" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K196" s="3" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="L196" s="3" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="M196" s="3" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="N196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="O196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="P196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="Q196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="R196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="S196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="T196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="U196" s="3" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="V196" s="3" t="s">
+        <x:v>526</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V195"/>
+  <x:autoFilter ref="A1:V196"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -15341,39 +15412,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>530</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>531</x:v>
+        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>532</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>533</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -15381,10 +15452,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>534</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>524</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
